--- a/tame_output/MOZAIC/bt/btc_vs_alt_20230726.xlsx
+++ b/tame_output/MOZAIC/bt/btc_vs_alt_20230726.xlsx
@@ -46138,7 +46138,7 @@
         <v>1.292711090871204</v>
       </c>
       <c r="D1758" t="n">
-        <v>1.149082867679284</v>
+        <v>1.149082867679285</v>
       </c>
       <c r="E1758" t="n">
         <v>1.220896979275244</v>
@@ -46193,7 +46193,7 @@
         <v>1.139282493633092</v>
       </c>
       <c r="E1760" t="n">
-        <v>1.205308317082621</v>
+        <v>1.205308317082622</v>
       </c>
       <c r="F1760" t="n">
         <v>4.217797936032158</v>
@@ -46202,7 +46202,7 @@
         <v>4.164977277272537</v>
       </c>
       <c r="H1760" t="n">
-        <v>4.191387606652338</v>
+        <v>4.191387606652339</v>
       </c>
     </row>
     <row r="1761">
@@ -46219,7 +46219,7 @@
         <v>1.130451033004338</v>
       </c>
       <c r="E1761" t="n">
-        <v>1.191053941750096</v>
+        <v>1.191053941750097</v>
       </c>
       <c r="F1761" t="n">
         <v>4.213729876698545</v>
@@ -46228,7 +46228,7 @@
         <v>4.16524754970194</v>
       </c>
       <c r="H1761" t="n">
-        <v>4.189488713200233</v>
+        <v>4.189488713200234</v>
       </c>
     </row>
     <row r="1762">
@@ -46254,7 +46254,7 @@
         <v>4.193374460286036</v>
       </c>
       <c r="H1762" t="n">
-        <v>4.215383444873702</v>
+        <v>4.215383444873703</v>
       </c>
     </row>
     <row r="1763">
@@ -46280,7 +46280,7 @@
         <v>4.15790977477116</v>
       </c>
       <c r="H1763" t="n">
-        <v>4.181345727333891</v>
+        <v>4.181345727333892</v>
       </c>
     </row>
     <row r="1764">
@@ -46306,7 +46306,7 @@
         <v>4.178037557602973</v>
       </c>
       <c r="H1764" t="n">
-        <v>4.201117621454369</v>
+        <v>4.20111762145437</v>
       </c>
     </row>
     <row r="1765">
@@ -46332,7 +46332,7 @@
         <v>4.28944141754862</v>
       </c>
       <c r="H1765" t="n">
-        <v>4.308274958376615</v>
+        <v>4.308274958376616</v>
       </c>
     </row>
     <row r="1766">
@@ -46358,7 +46358,7 @@
         <v>4.272248712685183</v>
       </c>
       <c r="H1766" t="n">
-        <v>4.292686816605752</v>
+        <v>4.292686816605753</v>
       </c>
     </row>
     <row r="1767">
@@ -46384,7 +46384,7 @@
         <v>4.279654676124383</v>
       </c>
       <c r="H1767" t="n">
-        <v>4.30090453529915</v>
+        <v>4.300904535299151</v>
       </c>
     </row>
     <row r="1768">
@@ -46410,7 +46410,7 @@
         <v>4.29148753597713</v>
       </c>
       <c r="H1768" t="n">
-        <v>4.311344936801001</v>
+        <v>4.311344936801002</v>
       </c>
     </row>
     <row r="1769">
@@ -46436,7 +46436,7 @@
         <v>4.269595496196809</v>
       </c>
       <c r="H1769" t="n">
-        <v>4.292684289485143</v>
+        <v>4.292684289485144</v>
       </c>
     </row>
     <row r="1770">
@@ -46462,7 +46462,7 @@
         <v>4.258320034591057</v>
       </c>
       <c r="H1770" t="n">
-        <v>4.283311826709043</v>
+        <v>4.283311826709044</v>
       </c>
     </row>
     <row r="1771">
@@ -46488,7 +46488,7 @@
         <v>4.288710793111602</v>
       </c>
       <c r="H1771" t="n">
-        <v>4.310075764599662</v>
+        <v>4.310075764599663</v>
       </c>
     </row>
     <row r="1772">
@@ -46514,7 +46514,7 @@
         <v>4.304200685145725</v>
       </c>
       <c r="H1772" t="n">
-        <v>4.326344125359333</v>
+        <v>4.326344125359334</v>
       </c>
     </row>
     <row r="1773">
@@ -46540,7 +46540,7 @@
         <v>4.289292419271062</v>
       </c>
       <c r="H1773" t="n">
-        <v>4.311843030499987</v>
+        <v>4.311843030499988</v>
       </c>
     </row>
     <row r="1774">
@@ -46566,7 +46566,7 @@
         <v>4.309328505926113</v>
       </c>
       <c r="H1774" t="n">
-        <v>4.333271892834957</v>
+        <v>4.333271892834958</v>
       </c>
     </row>
     <row r="1775">
@@ -46632,7 +46632,7 @@
         <v>1.147188430199636</v>
       </c>
       <c r="D1777" t="n">
-        <v>1.011868164275313</v>
+        <v>1.011868164275312</v>
       </c>
       <c r="E1777" t="n">
         <v>1.079528297237474</v>
@@ -46658,10 +46658,10 @@
         <v>1.142694932704834</v>
       </c>
       <c r="D1778" t="n">
-        <v>1.011868164275313</v>
+        <v>1.011868164275312</v>
       </c>
       <c r="E1778" t="n">
-        <v>1.077281548490074</v>
+        <v>1.077281548490073</v>
       </c>
       <c r="F1778" t="n">
         <v>4.327664091637725</v>
@@ -46684,10 +46684,10 @@
         <v>1.142694932704834</v>
       </c>
       <c r="D1779" t="n">
-        <v>1.011868164275313</v>
+        <v>1.011868164275312</v>
       </c>
       <c r="E1779" t="n">
-        <v>1.077281548490074</v>
+        <v>1.077281548490073</v>
       </c>
       <c r="F1779" t="n">
         <v>4.314471943890811</v>
@@ -46710,7 +46710,7 @@
         <v>1.142876535581554</v>
       </c>
       <c r="D1780" t="n">
-        <v>1.011868164275313</v>
+        <v>1.011868164275312</v>
       </c>
       <c r="E1780" t="n">
         <v>1.077372349928433</v>
@@ -46736,7 +46736,7 @@
         <v>1.145832117870097</v>
       </c>
       <c r="D1781" t="n">
-        <v>1.015999955921196</v>
+        <v>1.015999955921195</v>
       </c>
       <c r="E1781" t="n">
         <v>1.080916036895646</v>
@@ -46765,7 +46765,7 @@
         <v>1.017812999050428</v>
       </c>
       <c r="E1782" t="n">
-        <v>1.083073575145697</v>
+        <v>1.083073575145696</v>
       </c>
       <c r="F1782" t="n">
         <v>4.307842942635167</v>
@@ -46788,7 +46788,7 @@
         <v>1.149726033402624</v>
       </c>
       <c r="D1783" t="n">
-        <v>1.017700386675065</v>
+        <v>1.017700386675064</v>
       </c>
       <c r="E1783" t="n">
         <v>1.083713210038844</v>
@@ -46814,7 +46814,7 @@
         <v>1.161847716323109</v>
       </c>
       <c r="D1784" t="n">
-        <v>1.022304552383809</v>
+        <v>1.022304552383808</v>
       </c>
       <c r="E1784" t="n">
         <v>1.092076134353459</v>
@@ -46918,7 +46918,7 @@
         <v>1.154243653398535</v>
       </c>
       <c r="D1788" t="n">
-        <v>1.015175341285344</v>
+        <v>1.015175341285343</v>
       </c>
       <c r="E1788" t="n">
         <v>1.084709497341939</v>
@@ -46999,7 +46999,7 @@
         <v>1.009190118510188</v>
       </c>
       <c r="E1791" t="n">
-        <v>1.081199556652775</v>
+        <v>1.081199556652774</v>
       </c>
       <c r="F1791" t="n">
         <v>4.362615451280315</v>
@@ -47025,7 +47025,7 @@
         <v>1.010611022271277</v>
       </c>
       <c r="E1792" t="n">
-        <v>1.079944861679785</v>
+        <v>1.079944861679784</v>
       </c>
       <c r="F1792" t="n">
         <v>4.35299645551198</v>
@@ -47074,10 +47074,10 @@
         <v>1.139946695771346</v>
       </c>
       <c r="D1794" t="n">
-        <v>1.005868619378958</v>
+        <v>1.005868619378957</v>
       </c>
       <c r="E1794" t="n">
-        <v>1.072907657575152</v>
+        <v>1.072907657575151</v>
       </c>
       <c r="F1794" t="n">
         <v>4.355608378871554</v>
@@ -47100,7 +47100,7 @@
         <v>1.141189637043183</v>
       </c>
       <c r="D1795" t="n">
-        <v>1.007804168290574</v>
+        <v>1.007804168290573</v>
       </c>
       <c r="E1795" t="n">
         <v>1.074496902666878</v>
@@ -47126,7 +47126,7 @@
         <v>1.138909743357104</v>
       </c>
       <c r="D1796" t="n">
-        <v>1.007486640077208</v>
+        <v>1.007486640077207</v>
       </c>
       <c r="E1796" t="n">
         <v>1.073198191717156</v>
@@ -47152,7 +47152,7 @@
         <v>1.156200992818752</v>
       </c>
       <c r="D1797" t="n">
-        <v>1.013863759957143</v>
+        <v>1.013863759957142</v>
       </c>
       <c r="E1797" t="n">
         <v>1.085032376387947</v>
@@ -47207,7 +47207,7 @@
         <v>1.008426357105429</v>
       </c>
       <c r="E1799" t="n">
-        <v>1.081780459970159</v>
+        <v>1.081780459970158</v>
       </c>
       <c r="F1799" t="n">
         <v>4.368854018494178</v>
@@ -47230,7 +47230,7 @@
         <v>1.159027049762771</v>
       </c>
       <c r="D1800" t="n">
-        <v>1.011743815859747</v>
+        <v>1.011743815859746</v>
       </c>
       <c r="E1800" t="n">
         <v>1.085385432811259</v>
@@ -47256,7 +47256,7 @@
         <v>1.163577609375055</v>
       </c>
       <c r="D1801" t="n">
-        <v>1.013572978067695</v>
+        <v>1.013572978067694</v>
       </c>
       <c r="E1801" t="n">
         <v>1.088575293721375</v>
@@ -47282,10 +47282,10 @@
         <v>1.160000705383232</v>
       </c>
       <c r="D1802" t="n">
-        <v>1.012122787954502</v>
+        <v>1.012122787954501</v>
       </c>
       <c r="E1802" t="n">
-        <v>1.086061746668867</v>
+        <v>1.086061746668866</v>
       </c>
       <c r="F1802" t="n">
         <v>4.356115140348487</v>
@@ -47308,7 +47308,7 @@
         <v>1.165795263704313</v>
       </c>
       <c r="D1803" t="n">
-        <v>1.014947860865551</v>
+        <v>1.01494786086555</v>
       </c>
       <c r="E1803" t="n">
         <v>1.090371562284932</v>
@@ -47334,7 +47334,7 @@
         <v>1.170814218101672</v>
       </c>
       <c r="D1804" t="n">
-        <v>1.018951473467649</v>
+        <v>1.018951473467648</v>
       </c>
       <c r="E1804" t="n">
         <v>1.09488284578466</v>
@@ -47450,7 +47450,7 @@
         <v>4.316121505454637</v>
       </c>
       <c r="H1808" t="n">
-        <v>4.346493434995072</v>
+        <v>4.346493434995073</v>
       </c>
     </row>
     <row r="1809">
@@ -47476,7 +47476,7 @@
         <v>4.326604541708309</v>
       </c>
       <c r="H1809" t="n">
-        <v>4.357133817360126</v>
+        <v>4.357133817360127</v>
       </c>
     </row>
     <row r="1810">
@@ -47490,7 +47490,7 @@
         <v>1.215212258787296</v>
       </c>
       <c r="D1810" t="n">
-        <v>1.053108712472194</v>
+        <v>1.053108712472193</v>
       </c>
       <c r="E1810" t="n">
         <v>1.134160485629745</v>
@@ -47502,7 +47502,7 @@
         <v>4.368711262701396</v>
       </c>
       <c r="H1810" t="n">
-        <v>4.401131971964408</v>
+        <v>4.401131971964409</v>
       </c>
     </row>
     <row r="1811">
@@ -47516,7 +47516,7 @@
         <v>1.228019105926859</v>
       </c>
       <c r="D1811" t="n">
-        <v>1.059167466416125</v>
+        <v>1.059167466416124</v>
       </c>
       <c r="E1811" t="n">
         <v>1.143593286171492</v>
@@ -47528,7 +47528,7 @@
         <v>4.384461121469779</v>
       </c>
       <c r="H1811" t="n">
-        <v>4.418231449371918</v>
+        <v>4.418231449371919</v>
       </c>
     </row>
     <row r="1812">
@@ -47542,7 +47542,7 @@
         <v>1.226333168961271</v>
       </c>
       <c r="D1812" t="n">
-        <v>1.061422951974155</v>
+        <v>1.061422951974154</v>
       </c>
       <c r="E1812" t="n">
         <v>1.143878060467713</v>
@@ -47568,7 +47568,7 @@
         <v>1.265794727168105</v>
       </c>
       <c r="D1813" t="n">
-        <v>1.088095024324128</v>
+        <v>1.088095024324127</v>
       </c>
       <c r="E1813" t="n">
         <v>1.176944875746116</v>
@@ -47597,7 +47597,7 @@
         <v>1.075248342269472</v>
       </c>
       <c r="E1814" t="n">
-        <v>1.16391597256781</v>
+        <v>1.163915972567809</v>
       </c>
       <c r="F1814" t="n">
         <v>4.463000528855088</v>
@@ -47620,7 +47620,7 @@
         <v>1.254094167718103</v>
       </c>
       <c r="D1815" t="n">
-        <v>1.070835453866728</v>
+        <v>1.070835453866727</v>
       </c>
       <c r="E1815" t="n">
         <v>1.162464810792415</v>
@@ -47649,7 +47649,7 @@
         <v>1.093176859900679</v>
       </c>
       <c r="E1816" t="n">
-        <v>1.183412324946224</v>
+        <v>1.183412324946223</v>
       </c>
       <c r="F1816" t="n">
         <v>4.454530373911386</v>
@@ -47672,10 +47672,10 @@
         <v>1.26516686763698</v>
       </c>
       <c r="D1817" t="n">
-        <v>1.087636143923625</v>
+        <v>1.087636143923624</v>
       </c>
       <c r="E1817" t="n">
-        <v>1.176401505780303</v>
+        <v>1.176401505780302</v>
       </c>
       <c r="F1817" t="n">
         <v>4.473675303977001</v>
@@ -47727,7 +47727,7 @@
         <v>1.090029452513068</v>
       </c>
       <c r="E1819" t="n">
-        <v>1.178038066717217</v>
+        <v>1.178038066717216</v>
       </c>
       <c r="F1819" t="n">
         <v>4.457462836568324</v>
@@ -47736,7 +47736,7 @@
         <v>4.387055945205005</v>
       </c>
       <c r="H1819" t="n">
-        <v>4.422259390886657</v>
+        <v>4.422259390886656</v>
       </c>
     </row>
     <row r="1820">
@@ -47750,7 +47750,7 @@
         <v>1.26512774251818</v>
       </c>
       <c r="D1820" t="n">
-        <v>1.094541844747023</v>
+        <v>1.094541844747022</v>
       </c>
       <c r="E1820" t="n">
         <v>1.179834793632601</v>
@@ -47762,7 +47762,7 @@
         <v>4.382084111570906</v>
       </c>
       <c r="H1820" t="n">
-        <v>4.41620129112513</v>
+        <v>4.416201291125129</v>
       </c>
     </row>
     <row r="1821">
@@ -47788,7 +47788,7 @@
         <v>4.389911413577091</v>
       </c>
       <c r="H1821" t="n">
-        <v>4.423782539815775</v>
+        <v>4.423782539815774</v>
       </c>
     </row>
     <row r="1822">
@@ -47802,7 +47802,7 @@
         <v>1.266390731594857</v>
       </c>
       <c r="D1822" t="n">
-        <v>1.098004528880334</v>
+        <v>1.098004528880333</v>
       </c>
       <c r="E1822" t="n">
         <v>1.182197630237595</v>
@@ -47814,7 +47814,7 @@
         <v>4.398395957217421</v>
       </c>
       <c r="H1822" t="n">
-        <v>4.432073197760317</v>
+        <v>4.432073197760316</v>
       </c>
     </row>
     <row r="1823">
@@ -47828,7 +47828,7 @@
         <v>1.259316918925235</v>
       </c>
       <c r="D1823" t="n">
-        <v>1.097014305396309</v>
+        <v>1.097014305396308</v>
       </c>
       <c r="E1823" t="n">
         <v>1.178165612160772</v>
@@ -47866,7 +47866,7 @@
         <v>4.383877066996058</v>
       </c>
       <c r="H1824" t="n">
-        <v>4.41464345839089</v>
+        <v>4.414643458390889</v>
       </c>
     </row>
     <row r="1825">
@@ -47892,7 +47892,7 @@
         <v>4.391948373389536</v>
       </c>
       <c r="H1825" t="n">
-        <v>4.420755282856852</v>
+        <v>4.420755282856851</v>
       </c>
     </row>
     <row r="1826">
@@ -47918,7 +47918,7 @@
         <v>4.404455554522626</v>
       </c>
       <c r="H1826" t="n">
-        <v>4.433456695736757</v>
+        <v>4.433456695736756</v>
       </c>
     </row>
     <row r="1827">
@@ -47935,7 +47935,7 @@
         <v>1.125660829819563</v>
       </c>
       <c r="E1827" t="n">
-        <v>1.198234341234277</v>
+        <v>1.198234341234276</v>
       </c>
       <c r="F1827" t="n">
         <v>4.473246337825453</v>
@@ -47944,7 +47944,7 @@
         <v>4.415187528693679</v>
       </c>
       <c r="H1827" t="n">
-        <v>4.444216933259557</v>
+        <v>4.444216933259556</v>
       </c>
     </row>
     <row r="1828">
@@ -47970,7 +47970,7 @@
         <v>4.420256181320498</v>
       </c>
       <c r="H1828" t="n">
-        <v>4.450108508569709</v>
+        <v>4.450108508569708</v>
       </c>
     </row>
     <row r="1829">
@@ -47984,7 +47984,7 @@
         <v>1.258164631728269</v>
       </c>
       <c r="D1829" t="n">
-        <v>1.10982832889037</v>
+        <v>1.109828328890369</v>
       </c>
       <c r="E1829" t="n">
         <v>1.183996480309319</v>
@@ -47996,7 +47996,7 @@
         <v>4.425861061116874</v>
       </c>
       <c r="H1829" t="n">
-        <v>4.455528321684446</v>
+        <v>4.455528321684445</v>
       </c>
     </row>
     <row r="1830">
@@ -48022,7 +48022,7 @@
         <v>4.417434449334467</v>
       </c>
       <c r="H1830" t="n">
-        <v>4.446163771978664</v>
+        <v>4.446163771978663</v>
       </c>
     </row>
     <row r="1831">
@@ -48048,7 +48048,7 @@
         <v>4.418770671704691</v>
       </c>
       <c r="H1831" t="n">
-        <v>4.449775359450705</v>
+        <v>4.449775359450704</v>
       </c>
     </row>
     <row r="1832">
@@ -48074,7 +48074,7 @@
         <v>4.400601094108149</v>
       </c>
       <c r="H1832" t="n">
-        <v>4.431599001744756</v>
+        <v>4.431599001744755</v>
       </c>
     </row>
     <row r="1833">
@@ -48088,7 +48088,7 @@
         <v>1.240907185931621</v>
       </c>
       <c r="D1833" t="n">
-        <v>1.081377217229397</v>
+        <v>1.081377217229396</v>
       </c>
       <c r="E1833" t="n">
         <v>1.161142201580509</v>
@@ -48100,7 +48100,7 @@
         <v>4.3970891557154</v>
       </c>
       <c r="H1833" t="n">
-        <v>4.428995149455837</v>
+        <v>4.428995149455836</v>
       </c>
     </row>
     <row r="1834">
@@ -48117,7 +48117,7 @@
         <v>1.070738885581709</v>
       </c>
       <c r="E1834" t="n">
-        <v>1.153785258093166</v>
+        <v>1.153785258093165</v>
       </c>
       <c r="F1834" t="n">
         <v>4.477439602476156</v>
@@ -48126,7 +48126,7 @@
         <v>4.411002504466989</v>
       </c>
       <c r="H1834" t="n">
-        <v>4.444221053471563</v>
+        <v>4.444221053471562</v>
       </c>
     </row>
     <row r="1835">
@@ -48140,7 +48140,7 @@
         <v>1.235888283983474</v>
       </c>
       <c r="D1835" t="n">
-        <v>1.075209898974541</v>
+        <v>1.07520989897454</v>
       </c>
       <c r="E1835" t="n">
         <v>1.155549091479007</v>
@@ -48152,7 +48152,7 @@
         <v>4.401242313477941</v>
       </c>
       <c r="H1835" t="n">
-        <v>4.43337799047972</v>
+        <v>4.433377990479719</v>
       </c>
     </row>
     <row r="1836">
@@ -48166,10 +48166,10 @@
         <v>1.219427365428288</v>
       </c>
       <c r="D1836" t="n">
-        <v>1.060459670828319</v>
+        <v>1.060459670828318</v>
       </c>
       <c r="E1836" t="n">
-        <v>1.139943518128304</v>
+        <v>1.139943518128303</v>
       </c>
       <c r="F1836" t="n">
         <v>4.534390779701482</v>
@@ -48178,7 +48178,7 @@
         <v>4.470803701861493</v>
       </c>
       <c r="H1836" t="n">
-        <v>4.502597240781478</v>
+        <v>4.502597240781477</v>
       </c>
     </row>
     <row r="1837">
@@ -48192,7 +48192,7 @@
         <v>1.201631465135914</v>
       </c>
       <c r="D1837" t="n">
-        <v>1.03983526855141</v>
+        <v>1.039835268551409</v>
       </c>
       <c r="E1837" t="n">
         <v>1.120733366843662</v>
@@ -48204,7 +48204,7 @@
         <v>4.473883907531015</v>
       </c>
       <c r="H1837" t="n">
-        <v>4.506243146847908</v>
+        <v>4.506243146847907</v>
       </c>
     </row>
     <row r="1838">
@@ -48218,7 +48218,7 @@
         <v>1.205973589805724</v>
       </c>
       <c r="D1838" t="n">
-        <v>1.047268217561069</v>
+        <v>1.047268217561068</v>
       </c>
       <c r="E1838" t="n">
         <v>1.126620903683397</v>
@@ -48230,7 +48230,7 @@
         <v>4.489344552893488</v>
       </c>
       <c r="H1838" t="n">
-        <v>4.521085627342412</v>
+        <v>4.521085627342411</v>
       </c>
     </row>
     <row r="1839">
@@ -48256,7 +48256,7 @@
         <v>4.49910156369248</v>
       </c>
       <c r="H1839" t="n">
-        <v>4.531883078839139</v>
+        <v>4.531883078839138</v>
       </c>
     </row>
     <row r="1840">
@@ -48282,7 +48282,7 @@
         <v>4.517161416725437</v>
       </c>
       <c r="H1840" t="n">
-        <v>4.550609571281182</v>
+        <v>4.550609571281181</v>
       </c>
     </row>
     <row r="1841">
@@ -48299,7 +48299,7 @@
         <v>1.091417203080034</v>
       </c>
       <c r="E1841" t="n">
-        <v>1.175082343375018</v>
+        <v>1.175082343375017</v>
       </c>
       <c r="F1841" t="n">
         <v>4.61140382063077</v>
@@ -48308,7 +48308,7 @@
         <v>4.54447170839478</v>
       </c>
       <c r="H1841" t="n">
-        <v>4.577937764512766</v>
+        <v>4.577937764512765</v>
       </c>
     </row>
     <row r="1842">
@@ -48334,7 +48334,7 @@
         <v>4.610353701090677</v>
       </c>
       <c r="H1842" t="n">
-        <v>4.640205123751976</v>
+        <v>4.640205123751975</v>
       </c>
     </row>
     <row r="1843">
@@ -48386,7 +48386,7 @@
         <v>4.60972816159753</v>
       </c>
       <c r="H1844" t="n">
-        <v>4.640308988268507</v>
+        <v>4.640308988268506</v>
       </c>
     </row>
     <row r="1845">
@@ -48412,7 +48412,7 @@
         <v>4.59076593891868</v>
       </c>
       <c r="H1845" t="n">
-        <v>4.621212516750288</v>
+        <v>4.621212516750287</v>
       </c>
     </row>
     <row r="1846">
@@ -48429,7 +48429,7 @@
         <v>1.134414698932689</v>
       </c>
       <c r="E1846" t="n">
-        <v>1.211606446659193</v>
+        <v>1.211606446659192</v>
       </c>
       <c r="F1846" t="n">
         <v>4.630841886580179</v>
@@ -48438,7 +48438,7 @@
         <v>4.569088488398973</v>
       </c>
       <c r="H1846" t="n">
-        <v>4.599965187489567</v>
+        <v>4.599965187489566</v>
       </c>
     </row>
     <row r="1847">
@@ -48452,7 +48452,7 @@
         <v>1.28270550705608</v>
       </c>
       <c r="D1847" t="n">
-        <v>1.133219035631951</v>
+        <v>1.13321903563195</v>
       </c>
       <c r="E1847" t="n">
         <v>1.207962271344015</v>
@@ -48464,7 +48464,7 @@
         <v>4.587931094747802</v>
       </c>
       <c r="H1847" t="n">
-        <v>4.617828389032621</v>
+        <v>4.617828389032619</v>
       </c>
     </row>
     <row r="1848">
@@ -48478,7 +48478,7 @@
         <v>1.291015825758161</v>
       </c>
       <c r="D1848" t="n">
-        <v>1.14951160513919</v>
+        <v>1.149511605139189</v>
       </c>
       <c r="E1848" t="n">
         <v>1.220263715448675</v>
@@ -48504,7 +48504,7 @@
         <v>1.305478988924979</v>
       </c>
       <c r="D1849" t="n">
-        <v>1.163553032553382</v>
+        <v>1.163553032553381</v>
       </c>
       <c r="E1849" t="n">
         <v>1.23451601073918</v>
@@ -48516,7 +48516,7 @@
         <v>4.738334603028161</v>
       </c>
       <c r="H1849" t="n">
-        <v>4.766719794302473</v>
+        <v>4.766719794302472</v>
       </c>
     </row>
     <row r="1850">
@@ -48582,7 +48582,7 @@
         <v>1.315865769079089</v>
       </c>
       <c r="D1852" t="n">
-        <v>1.176019947561268</v>
+        <v>1.176019947561267</v>
       </c>
       <c r="E1852" t="n">
         <v>1.245942858320178</v>
@@ -48608,10 +48608,10 @@
         <v>1.306007556483216</v>
       </c>
       <c r="D1853" t="n">
-        <v>1.162453516010533</v>
+        <v>1.162453516010532</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.234230536246875</v>
+        <v>1.234230536246874</v>
       </c>
       <c r="F1853" t="n">
         <v>4.83285429179749</v>
@@ -48620,7 +48620,7 @@
         <v>4.775432675608414</v>
       </c>
       <c r="H1853" t="n">
-        <v>4.804143483702943</v>
+        <v>4.804143483702942</v>
       </c>
     </row>
     <row r="1854">
@@ -48646,7 +48646,7 @@
         <v>4.754400740566083</v>
       </c>
       <c r="H1854" t="n">
-        <v>4.782446909749516</v>
+        <v>4.782446909749515</v>
       </c>
     </row>
     <row r="1855">
@@ -48660,7 +48660,7 @@
         <v>1.28176095340165</v>
       </c>
       <c r="D1855" t="n">
-        <v>1.13011375746012</v>
+        <v>1.130113757460119</v>
       </c>
       <c r="E1855" t="n">
         <v>1.205937355430885</v>
@@ -48672,7 +48672,7 @@
         <v>4.75880004713821</v>
       </c>
       <c r="H1855" t="n">
-        <v>4.789129486326509</v>
+        <v>4.789129486326508</v>
       </c>
     </row>
     <row r="1856">
@@ -48686,7 +48686,7 @@
         <v>1.279632510883795</v>
       </c>
       <c r="D1856" t="n">
-        <v>1.135353437942193</v>
+        <v>1.135353437942192</v>
       </c>
       <c r="E1856" t="n">
         <v>1.207492974412994</v>
@@ -48698,7 +48698,7 @@
         <v>4.744011924035995</v>
       </c>
       <c r="H1856" t="n">
-        <v>4.772867738624309</v>
+        <v>4.772867738624308</v>
       </c>
     </row>
     <row r="1857">
@@ -48767,7 +48767,7 @@
         <v>1.140765645030162</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.209455103936218</v>
+        <v>1.209455103936217</v>
       </c>
       <c r="F1859" t="n">
         <v>4.778750190885203</v>
@@ -48793,7 +48793,7 @@
         <v>1.132082962514532</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.207411652920813</v>
+        <v>1.207411652920812</v>
       </c>
       <c r="F1860" t="n">
         <v>4.805682869613731</v>
@@ -48816,7 +48816,7 @@
         <v>1.272453916448067</v>
       </c>
       <c r="D1861" t="n">
-        <v>1.121365188289546</v>
+        <v>1.121365188289545</v>
       </c>
       <c r="E1861" t="n">
         <v>1.196909552368806</v>
@@ -48894,7 +48894,7 @@
         <v>1.219925866228818</v>
       </c>
       <c r="D1864" t="n">
-        <v>1.082442311738481</v>
+        <v>1.08244231173848</v>
       </c>
       <c r="E1864" t="n">
         <v>1.151184088983649</v>
@@ -48946,7 +48946,7 @@
         <v>1.213180582565608</v>
       </c>
       <c r="D1866" t="n">
-        <v>1.071427966968301</v>
+        <v>1.0714279669683</v>
       </c>
       <c r="E1866" t="n">
         <v>1.142304274766954</v>
@@ -48972,7 +48972,7 @@
         <v>1.212949419946158</v>
       </c>
       <c r="D1867" t="n">
-        <v>1.062588253197514</v>
+        <v>1.062588253197513</v>
       </c>
       <c r="E1867" t="n">
         <v>1.137768836571836</v>
@@ -49050,7 +49050,7 @@
         <v>1.228264891040578</v>
       </c>
       <c r="D1870" t="n">
-        <v>1.06831231543489</v>
+        <v>1.068312315434889</v>
       </c>
       <c r="E1870" t="n">
         <v>1.148288603237734</v>
@@ -49076,7 +49076,7 @@
         <v>1.231920966487894</v>
       </c>
       <c r="D1871" t="n">
-        <v>1.072145554249143</v>
+        <v>1.072145554249142</v>
       </c>
       <c r="E1871" t="n">
         <v>1.152033260368518</v>
@@ -49131,7 +49131,7 @@
         <v>1.07386720002008</v>
       </c>
       <c r="E1873" t="n">
-        <v>1.155320636783403</v>
+        <v>1.155320636783402</v>
       </c>
       <c r="F1873" t="n">
         <v>4.726631322409664</v>
@@ -49157,7 +49157,7 @@
         <v>1.106685732890069</v>
       </c>
       <c r="E1874" t="n">
-        <v>1.18795976873036</v>
+        <v>1.187959768730359</v>
       </c>
       <c r="F1874" t="n">
         <v>4.766884843691045</v>
@@ -49180,7 +49180,7 @@
         <v>1.269302277343165</v>
       </c>
       <c r="D1875" t="n">
-        <v>1.114160445042292</v>
+        <v>1.114160445042291</v>
       </c>
       <c r="E1875" t="n">
         <v>1.191731361192728</v>
@@ -49215,7 +49215,7 @@
         <v>4.788682309588918</v>
       </c>
       <c r="G1876" t="n">
-        <v>4.731696700239209</v>
+        <v>4.73169670023921</v>
       </c>
       <c r="H1876" t="n">
         <v>4.760189504914055</v>
@@ -49258,16 +49258,16 @@
         <v>1.235632044424666</v>
       </c>
       <c r="D1878" t="n">
-        <v>1.086328441016695</v>
+        <v>1.086328441016694</v>
       </c>
       <c r="E1878" t="n">
-        <v>1.160980242720681</v>
+        <v>1.16098024272068</v>
       </c>
       <c r="F1878" t="n">
         <v>4.784231604158671</v>
       </c>
       <c r="G1878" t="n">
-        <v>4.724510162795478</v>
+        <v>4.724510162795479</v>
       </c>
       <c r="H1878" t="n">
         <v>4.754370883477065</v>
@@ -49284,7 +49284,7 @@
         <v>1.238996299064537</v>
       </c>
       <c r="D1879" t="n">
-        <v>1.091749762854129</v>
+        <v>1.091749762854128</v>
       </c>
       <c r="E1879" t="n">
         <v>1.165373030959333</v>
@@ -49293,7 +49293,7 @@
         <v>4.803606478065434</v>
       </c>
       <c r="G1879" t="n">
-        <v>4.744707863581266</v>
+        <v>4.744707863581267</v>
       </c>
       <c r="H1879" t="n">
         <v>4.774157170823341</v>
@@ -49319,7 +49319,7 @@
         <v>4.77780523878372</v>
       </c>
       <c r="G1880" t="n">
-        <v>4.71783958944361</v>
+        <v>4.717839589443611</v>
       </c>
       <c r="H1880" t="n">
         <v>4.747822414113656</v>
@@ -49339,13 +49339,13 @@
         <v>1.092214788098179</v>
       </c>
       <c r="E1881" t="n">
-        <v>1.166864905941296</v>
+        <v>1.166864905941295</v>
       </c>
       <c r="F1881" t="n">
         <v>4.762394976629363</v>
       </c>
       <c r="G1881" t="n">
-        <v>4.702674882354866</v>
+        <v>4.702674882354867</v>
       </c>
       <c r="H1881" t="n">
         <v>4.732534929492106</v>
@@ -49388,7 +49388,7 @@
         <v>1.246948949981624</v>
       </c>
       <c r="D1883" t="n">
-        <v>1.093822444691955</v>
+        <v>1.093822444691954</v>
       </c>
       <c r="E1883" t="n">
         <v>1.170385697336789</v>
@@ -49397,7 +49397,7 @@
         <v>4.720766958317274</v>
       </c>
       <c r="G1883" t="n">
-        <v>4.659516356201402</v>
+        <v>4.659516356201403</v>
       </c>
       <c r="H1883" t="n">
         <v>4.690141657259328</v>
@@ -49417,13 +49417,13 @@
         <v>1.101184957211709</v>
       </c>
       <c r="E1884" t="n">
-        <v>1.176142813133071</v>
+        <v>1.17614281313307</v>
       </c>
       <c r="F1884" t="n">
         <v>4.710388690334873</v>
       </c>
       <c r="G1884" t="n">
-        <v>4.650422405597779</v>
+        <v>4.65042240559778</v>
       </c>
       <c r="H1884" t="n">
         <v>4.680405547966316</v>
@@ -49449,7 +49449,7 @@
         <v>4.730954584257963</v>
       </c>
       <c r="G1885" t="n">
-        <v>4.669124625302256</v>
+        <v>4.669124625302257</v>
       </c>
       <c r="H1885" t="n">
         <v>4.7000396047801</v>
@@ -49475,7 +49475,7 @@
         <v>4.738799713838161</v>
       </c>
       <c r="G1886" t="n">
-        <v>4.677543195509149</v>
+        <v>4.67754319550915</v>
       </c>
       <c r="H1886" t="n">
         <v>4.708171454673646</v>
@@ -49501,7 +49501,7 @@
         <v>4.714804364111681</v>
       </c>
       <c r="G1887" t="n">
-        <v>4.653314195990144</v>
+        <v>4.653314195990145</v>
       </c>
       <c r="H1887" t="n">
         <v>4.684059280050903</v>
@@ -49527,7 +49527,7 @@
         <v>4.725812226750948</v>
       </c>
       <c r="G1888" t="n">
-        <v>4.663423130361185</v>
+        <v>4.663423130361186</v>
       </c>
       <c r="H1888" t="n">
         <v>4.694617678556057</v>
@@ -49553,7 +49553,7 @@
         <v>4.722607328250432</v>
       </c>
       <c r="G1889" t="n">
-        <v>4.660818907250627</v>
+        <v>4.660818907250629</v>
       </c>
       <c r="H1889" t="n">
         <v>4.69171311775052</v>
@@ -49579,7 +49579,7 @@
         <v>4.689442835560055</v>
       </c>
       <c r="G1890" t="n">
-        <v>4.629785925195621</v>
+        <v>4.629785925195622</v>
       </c>
       <c r="H1890" t="n">
         <v>4.659614380377829</v>
@@ -49605,7 +49605,7 @@
         <v>4.67490542100013</v>
       </c>
       <c r="G1891" t="n">
-        <v>4.615897114750023</v>
+        <v>4.615897114750025</v>
       </c>
       <c r="H1891" t="n">
         <v>4.645401267875068</v>
@@ -49631,7 +49631,7 @@
         <v>4.679407557619235</v>
       </c>
       <c r="G1892" t="n">
-        <v>4.617607999181502</v>
+        <v>4.617607999181504</v>
       </c>
       <c r="H1892" t="n">
         <v>4.64850777840036</v>
@@ -49657,7 +49657,7 @@
         <v>4.678992056330803</v>
       </c>
       <c r="G1893" t="n">
-        <v>4.616503848374106</v>
+        <v>4.616503848374108</v>
       </c>
       <c r="H1893" t="n">
         <v>4.647747952352446</v>
@@ -49683,7 +49683,7 @@
         <v>4.670297618346368</v>
       </c>
       <c r="G1894" t="n">
-        <v>4.608303301776349</v>
+        <v>4.608303301776351</v>
       </c>
       <c r="H1894" t="n">
         <v>4.639300460061349</v>
@@ -49709,7 +49709,7 @@
         <v>4.673593651746551</v>
       </c>
       <c r="G1895" t="n">
-        <v>4.610712510140464</v>
+        <v>4.610712510140466</v>
       </c>
       <c r="H1895" t="n">
         <v>4.642153080943499</v>
@@ -49735,7 +49735,7 @@
         <v>4.633356787724041</v>
       </c>
       <c r="G1896" t="n">
-        <v>4.574383865802555</v>
+        <v>4.574383865802557</v>
       </c>
       <c r="H1896" t="n">
         <v>4.603870326763289</v>
@@ -49761,7 +49761,7 @@
         <v>4.610760711810325</v>
       </c>
       <c r="G1897" t="n">
-        <v>4.554719366412554</v>
+        <v>4.554719366412556</v>
       </c>
       <c r="H1897" t="n">
         <v>4.582740039111431</v>
@@ -49787,7 +49787,7 @@
         <v>4.603670575724087</v>
       </c>
       <c r="G1898" t="n">
-        <v>4.549060348364906</v>
+        <v>4.549060348364907</v>
       </c>
       <c r="H1898" t="n">
         <v>4.576365462044488</v>
@@ -49813,7 +49813,7 @@
         <v>4.612009653039527</v>
       </c>
       <c r="G1899" t="n">
-        <v>4.555856402603762</v>
+        <v>4.555856402603764</v>
       </c>
       <c r="H1899" t="n">
         <v>4.583933027821637</v>
@@ -49839,7 +49839,7 @@
         <v>4.653471700763832</v>
       </c>
       <c r="G1900" t="n">
-        <v>4.599061092495012</v>
+        <v>4.599061092495014</v>
       </c>
       <c r="H1900" t="n">
         <v>4.626266396629415</v>
@@ -49865,7 +49865,7 @@
         <v>4.66346447057604</v>
       </c>
       <c r="G1901" t="n">
-        <v>4.605796145811949</v>
+        <v>4.605796145811951</v>
       </c>
       <c r="H1901" t="n">
         <v>4.634630308193987</v>
@@ -49891,7 +49891,7 @@
         <v>4.653800772917777</v>
       </c>
       <c r="G1902" t="n">
-        <v>4.596122914696079</v>
+        <v>4.596122914696081</v>
       </c>
       <c r="H1902" t="n">
         <v>4.624961843806921</v>
@@ -49917,7 +49917,7 @@
         <v>4.675135642170253</v>
       </c>
       <c r="G1903" t="n">
-        <v>4.619883506104603</v>
+        <v>4.619883506104605</v>
       </c>
       <c r="H1903" t="n">
         <v>4.647509574137421</v>
@@ -49943,7 +49943,7 @@
         <v>4.722903580730891</v>
       </c>
       <c r="G1904" t="n">
-        <v>4.667001667302091</v>
+        <v>4.667001667302093</v>
       </c>
       <c r="H1904" t="n">
         <v>4.694952624016483</v>
@@ -49969,7 +49969,7 @@
         <v>4.710900628168497</v>
       </c>
       <c r="G1905" t="n">
-        <v>4.65536838169262</v>
+        <v>4.655368381692622</v>
       </c>
       <c r="H1905" t="n">
         <v>4.683134504930551</v>
@@ -49995,7 +49995,7 @@
         <v>4.736523273236282</v>
       </c>
       <c r="G1906" t="n">
-        <v>4.681788303878293</v>
+        <v>4.681788303878295</v>
       </c>
       <c r="H1906" t="n">
         <v>4.709155788557279</v>
@@ -50021,7 +50021,7 @@
         <v>4.732067783947153</v>
       </c>
       <c r="G1907" t="n">
-        <v>4.677740686659741</v>
+        <v>4.677740686659742</v>
       </c>
       <c r="H1907" t="n">
         <v>4.704904235303438</v>
@@ -50047,7 +50047,7 @@
         <v>4.71455293174147</v>
       </c>
       <c r="G1908" t="n">
-        <v>4.667467291861959</v>
+        <v>4.667467291861961</v>
       </c>
       <c r="H1908" t="n">
         <v>4.691010111801705</v>
@@ -50073,7 +50073,7 @@
         <v>4.673529079852671</v>
       </c>
       <c r="G1909" t="n">
-        <v>4.624520484050313</v>
+        <v>4.624520484050315</v>
       </c>
       <c r="H1909" t="n">
         <v>4.649024781951483</v>
@@ -50099,7 +50099,7 @@
         <v>4.695779363549252</v>
       </c>
       <c r="G1910" t="n">
-        <v>4.648530335811475</v>
+        <v>4.648530335811476</v>
       </c>
       <c r="H1910" t="n">
         <v>4.672154849680354</v>
@@ -50125,7 +50125,7 @@
         <v>4.678669293733892</v>
       </c>
       <c r="G1911" t="n">
-        <v>4.628843233165785</v>
+        <v>4.628843233165787</v>
       </c>
       <c r="H1911" t="n">
         <v>4.65375626344983</v>
@@ -50151,7 +50151,7 @@
         <v>4.69229150632612</v>
       </c>
       <c r="G1912" t="n">
-        <v>4.642359221836154</v>
+        <v>4.642359221836156</v>
       </c>
       <c r="H1912" t="n">
         <v>4.667325364081128</v>
@@ -50177,7 +50177,7 @@
         <v>4.69917130988409</v>
       </c>
       <c r="G1913" t="n">
-        <v>4.649957825637269</v>
+        <v>4.649957825637271</v>
       </c>
       <c r="H1913" t="n">
         <v>4.674564567760671</v>
@@ -50203,7 +50203,7 @@
         <v>4.697656492554525</v>
       </c>
       <c r="G1914" t="n">
-        <v>4.647861264114622</v>
+        <v>4.647861264114624</v>
       </c>
       <c r="H1914" t="n">
         <v>4.672758878334565</v>
@@ -50229,7 +50229,7 @@
         <v>4.713624777879459</v>
       </c>
       <c r="G1915" t="n">
-        <v>4.66624195346518</v>
+        <v>4.666241953465182</v>
       </c>
       <c r="H1915" t="n">
         <v>4.689933365672311</v>
@@ -50255,7 +50255,7 @@
         <v>4.742569994023495</v>
       </c>
       <c r="G1916" t="n">
-        <v>4.695594895697322</v>
+        <v>4.695594895697324</v>
       </c>
       <c r="H1916" t="n">
         <v>4.7190824448604</v>
@@ -50281,7 +50281,7 @@
         <v>4.747571444170468</v>
       </c>
       <c r="G1917" t="n">
-        <v>4.700564763263899</v>
+        <v>4.700564763263901</v>
       </c>
       <c r="H1917" t="n">
         <v>4.724068103717175</v>
@@ -50307,7 +50307,7 @@
         <v>4.771461821506808</v>
       </c>
       <c r="G1918" t="n">
-        <v>4.724694881945734</v>
+        <v>4.724694881945736</v>
       </c>
       <c r="H1918" t="n">
         <v>4.748078351726262</v>
@@ -50333,7 +50333,7 @@
         <v>4.750070234166123</v>
       </c>
       <c r="G1919" t="n">
-        <v>4.701370474881924</v>
+        <v>4.701370474881926</v>
       </c>
       <c r="H1919" t="n">
         <v>4.725720354524015</v>
@@ -50359,7 +50359,7 @@
         <v>4.745661580035651</v>
       </c>
       <c r="G1920" t="n">
-        <v>4.698792670316982</v>
+        <v>4.698792670316984</v>
       </c>
       <c r="H1920" t="n">
         <v>4.722227125176308</v>
@@ -50385,7 +50385,7 @@
         <v>4.718523869308713</v>
       </c>
       <c r="G1921" t="n">
-        <v>4.673981489342854</v>
+        <v>4.673981489342856</v>
       </c>
       <c r="H1921" t="n">
         <v>4.696252679325775</v>
@@ -50411,7 +50411,7 @@
         <v>4.71080725684447</v>
       </c>
       <c r="G1922" t="n">
-        <v>4.667141141398046</v>
+        <v>4.667141141398048</v>
       </c>
       <c r="H1922" t="n">
         <v>4.688974199121249</v>
@@ -50437,7 +50437,7 @@
         <v>4.707317360331963</v>
       </c>
       <c r="G1923" t="n">
-        <v>4.663833647076296</v>
+        <v>4.663833647076298</v>
       </c>
       <c r="H1923" t="n">
         <v>4.685575503704121</v>
@@ -50463,7 +50463,7 @@
         <v>4.693606083176805</v>
       </c>
       <c r="G1924" t="n">
-        <v>4.648122345063499</v>
+        <v>4.6481223450635</v>
       </c>
       <c r="H1924" t="n">
         <v>4.670864214120143</v>
@@ -50489,7 +50489,7 @@
         <v>4.696029118590364</v>
       </c>
       <c r="G1925" t="n">
-        <v>4.649348390058082</v>
+        <v>4.649348390058083</v>
       </c>
       <c r="H1925" t="n">
         <v>4.672688754324214</v>
@@ -50515,7 +50515,7 @@
         <v>4.68909181326342</v>
       </c>
       <c r="G1926" t="n">
-        <v>4.642637390836381</v>
+        <v>4.642637390836382</v>
       </c>
       <c r="H1926" t="n">
         <v>4.665864602049892</v>
@@ -50541,7 +50541,7 @@
         <v>4.697794704136211</v>
       </c>
       <c r="G1927" t="n">
-        <v>4.651791613628468</v>
+        <v>4.65179161362847</v>
       </c>
       <c r="H1927" t="n">
         <v>4.674793158882331</v>
@@ -50567,7 +50567,7 @@
         <v>4.719659852361632</v>
       </c>
       <c r="G1928" t="n">
-        <v>4.673527149420767</v>
+        <v>4.673527149420769</v>
       </c>
       <c r="H1928" t="n">
         <v>4.696593500891192</v>
@@ -50593,7 +50593,7 @@
         <v>4.723031364719819</v>
       </c>
       <c r="G1929" t="n">
-        <v>4.678440207504215</v>
+        <v>4.678440207504217</v>
       </c>
       <c r="H1929" t="n">
         <v>4.700735786112008</v>
@@ -50619,7 +50619,7 @@
         <v>4.718716334184196</v>
       </c>
       <c r="G1930" t="n">
-        <v>4.674090185318553</v>
+        <v>4.674090185318555</v>
       </c>
       <c r="H1930" t="n">
         <v>4.696403259751366</v>
@@ -50645,7 +50645,7 @@
         <v>4.719358251534736</v>
       </c>
       <c r="G1931" t="n">
-        <v>4.677301258381029</v>
+        <v>4.677301258381031</v>
       </c>
       <c r="H1931" t="n">
         <v>4.698329754957874</v>
@@ -50671,7 +50671,7 @@
         <v>4.727047226541046</v>
       </c>
       <c r="G1932" t="n">
-        <v>4.685044099362944</v>
+        <v>4.685044099362946</v>
       </c>
       <c r="H1932" t="n">
         <v>4.706045662951986</v>
@@ -50697,7 +50697,7 @@
         <v>4.726206026678454</v>
       </c>
       <c r="G1933" t="n">
-        <v>4.684880782735648</v>
+        <v>4.684880782735649</v>
       </c>
       <c r="H1933" t="n">
         <v>4.705543404707042</v>
@@ -50723,7 +50723,7 @@
         <v>4.729034130665411</v>
       </c>
       <c r="G1934" t="n">
-        <v>4.688955253526885</v>
+        <v>4.688955253526887</v>
       </c>
       <c r="H1934" t="n">
         <v>4.708994692096139</v>
@@ -50749,7 +50749,7 @@
         <v>4.712180789422315</v>
       </c>
       <c r="G1935" t="n">
-        <v>4.669865737974894</v>
+        <v>4.669865737974896</v>
       </c>
       <c r="H1935" t="n">
         <v>4.691023263698596</v>
@@ -50775,7 +50775,7 @@
         <v>4.7522814314089</v>
       </c>
       <c r="G1936" t="n">
-        <v>4.708119998978777</v>
+        <v>4.708119998978779</v>
       </c>
       <c r="H1936" t="n">
         <v>4.730200715193829</v>
@@ -50801,7 +50801,7 @@
         <v>4.68241115957288</v>
       </c>
       <c r="G1937" t="n">
-        <v>4.635489641997718</v>
+        <v>4.63548964199772</v>
       </c>
       <c r="H1937" t="n">
         <v>4.65895040078529</v>
@@ -50827,7 +50827,7 @@
         <v>4.654870208418752</v>
       </c>
       <c r="G1938" t="n">
-        <v>4.605330061823878</v>
+        <v>4.60533006182388</v>
       </c>
       <c r="H1938" t="n">
         <v>4.630100135121307</v>
@@ -50853,7 +50853,7 @@
         <v>4.61715823102208</v>
       </c>
       <c r="G1939" t="n">
-        <v>4.569308711041357</v>
+        <v>4.569308711041359</v>
       </c>
       <c r="H1939" t="n">
         <v>4.59323347103171</v>
@@ -50879,7 +50879,7 @@
         <v>4.623183364890926</v>
       </c>
       <c r="G1940" t="n">
-        <v>4.577988643153359</v>
+        <v>4.577988643153361</v>
       </c>
       <c r="H1940" t="n">
         <v>4.600586004022134</v>
@@ -50905,7 +50905,7 @@
         <v>4.61385217881093</v>
       </c>
       <c r="G1941" t="n">
-        <v>4.569407803179926</v>
+        <v>4.569407803179928</v>
       </c>
       <c r="H1941" t="n">
         <v>4.591629990995419</v>
@@ -50931,7 +50931,7 @@
         <v>4.610394719927227</v>
       </c>
       <c r="G1942" t="n">
-        <v>4.563797621875533</v>
+        <v>4.563797621875535</v>
       </c>
       <c r="H1942" t="n">
         <v>4.587096170901371</v>
@@ -50957,7 +50957,7 @@
         <v>4.626781087366446</v>
       </c>
       <c r="G1943" t="n">
-        <v>4.57951130474003</v>
+        <v>4.579511304740032</v>
       </c>
       <c r="H1943" t="n">
         <v>4.603146196053229</v>
@@ -50983,7 +50983,7 @@
         <v>4.626116168003535</v>
       </c>
       <c r="G1944" t="n">
-        <v>4.578642754027296</v>
+        <v>4.578642754027298</v>
       </c>
       <c r="H1944" t="n">
         <v>4.602379461015407</v>
@@ -51009,7 +51009,7 @@
         <v>4.651968982632669</v>
       </c>
       <c r="G1945" t="n">
-        <v>4.603846284538541</v>
+        <v>4.603846284538543</v>
       </c>
       <c r="H1945" t="n">
         <v>4.627907633585597</v>
@@ -51035,7 +51035,7 @@
         <v>4.656987967538759</v>
       </c>
       <c r="G1946" t="n">
-        <v>4.610083333598873</v>
+        <v>4.610083333598875</v>
       </c>
       <c r="H1946" t="n">
         <v>4.633535650568808</v>
@@ -51061,7 +51061,7 @@
         <v>4.662565862603856</v>
       </c>
       <c r="G1947" t="n">
-        <v>4.613491080527811</v>
+        <v>4.613491080527813</v>
       </c>
       <c r="H1947" t="n">
         <v>4.638028471565825</v>
@@ -51087,7 +51087,7 @@
         <v>4.659359445814687</v>
       </c>
       <c r="G1948" t="n">
-        <v>4.61181865514413</v>
+        <v>4.611818655144131</v>
       </c>
       <c r="H1948" t="n">
         <v>4.6355890504794</v>
@@ -51113,7 +51113,7 @@
         <v>4.612897664640801</v>
       </c>
       <c r="G1949" t="n">
-        <v>4.565148515852226</v>
+        <v>4.565148515852227</v>
       </c>
       <c r="H1949" t="n">
         <v>4.589023090246505</v>
@@ -51139,7 +51139,7 @@
         <v>4.611067358914148</v>
       </c>
       <c r="G1950" t="n">
-        <v>4.565076843972354</v>
+        <v>4.565076843972355</v>
       </c>
       <c r="H1950" t="n">
         <v>4.588072101443242</v>
@@ -51165,7 +51165,7 @@
         <v>4.618733362772155</v>
       </c>
       <c r="G1951" t="n">
-        <v>4.572973828628145</v>
+        <v>4.572973828628147</v>
       </c>
       <c r="H1951" t="n">
         <v>4.595853595700141</v>
@@ -51191,7 +51191,7 @@
         <v>4.617681228446657</v>
       </c>
       <c r="G1952" t="n">
-        <v>4.572945754630721</v>
+        <v>4.572945754630723</v>
       </c>
       <c r="H1952" t="n">
         <v>4.59531349153868</v>
@@ -51217,7 +51217,7 @@
         <v>4.626928099963806</v>
       </c>
       <c r="G1953" t="n">
-        <v>4.582918538788816</v>
+        <v>4.582918538788818</v>
       </c>
       <c r="H1953" t="n">
         <v>4.604923319376302</v>
@@ -51243,7 +51243,7 @@
         <v>4.610631634456432</v>
       </c>
       <c r="G1954" t="n">
-        <v>4.566608738598471</v>
+        <v>4.566608738598473</v>
       </c>
       <c r="H1954" t="n">
         <v>4.588620186527442</v>
@@ -51269,7 +51269,7 @@
         <v>4.602601640753814</v>
       </c>
       <c r="G1955" t="n">
-        <v>4.558541823986481</v>
+        <v>4.558541823986483</v>
       </c>
       <c r="H1955" t="n">
         <v>4.580571732370138</v>
@@ -51295,7 +51295,7 @@
         <v>4.599587593311211</v>
       </c>
       <c r="G1956" t="n">
-        <v>4.555372889268783</v>
+        <v>4.555372889268785</v>
       </c>
       <c r="H1956" t="n">
         <v>4.577480241289988</v>
@@ -51321,7 +51321,7 @@
         <v>4.604124281851925</v>
       </c>
       <c r="G1957" t="n">
-        <v>4.558805278053965</v>
+        <v>4.558805278053967</v>
       </c>
       <c r="H1957" t="n">
         <v>4.581464779952936</v>
@@ -51347,7 +51347,7 @@
         <v>4.587423716701972</v>
       </c>
       <c r="G1958" t="n">
-        <v>4.541429104652187</v>
+        <v>4.541429104652189</v>
       </c>
       <c r="H1958" t="n">
         <v>4.56442641067707</v>
@@ -51373,7 +51373,7 @@
         <v>4.578389283389882</v>
       </c>
       <c r="G1959" t="n">
-        <v>4.531265981777745</v>
+        <v>4.531265981777747</v>
       </c>
       <c r="H1959" t="n">
         <v>4.554827632583804</v>
@@ -51399,7 +51399,7 @@
         <v>4.574640792830579</v>
       </c>
       <c r="G1960" t="n">
-        <v>4.527580921748812</v>
+        <v>4.527580921748814</v>
       </c>
       <c r="H1960" t="n">
         <v>4.551110857289685</v>
@@ -51425,7 +51425,7 @@
         <v>4.583536371706302</v>
       </c>
       <c r="G1961" t="n">
-        <v>4.531584219648001</v>
+        <v>4.531584219648003</v>
       </c>
       <c r="H1961" t="n">
         <v>4.557560295677141</v>
@@ -51451,7 +51451,7 @@
         <v>4.583486503293081</v>
       </c>
       <c r="G1962" t="n">
-        <v>4.532258491517594</v>
+        <v>4.532258491517596</v>
       </c>
       <c r="H1962" t="n">
         <v>4.557872497405327</v>
@@ -51477,7 +51477,7 @@
         <v>4.586209936494321</v>
       </c>
       <c r="G1963" t="n">
-        <v>4.534299116767288</v>
+        <v>4.53429911676729</v>
       </c>
       <c r="H1963" t="n">
         <v>4.560254526630795</v>
@@ -51503,7 +51503,7 @@
         <v>4.588836121509279</v>
       </c>
       <c r="G1964" t="n">
-        <v>4.536949084575641</v>
+        <v>4.536949084575642</v>
       </c>
       <c r="H1964" t="n">
         <v>4.562892603042449</v>
@@ -51529,7 +51529,7 @@
         <v>4.591099815892531</v>
       </c>
       <c r="G1965" t="n">
-        <v>4.543039082997535</v>
+        <v>4.543039082997537</v>
       </c>
       <c r="H1965" t="n">
         <v>4.567069449445023</v>
@@ -51555,7 +51555,7 @@
         <v>4.576334026513421</v>
       </c>
       <c r="G1966" t="n">
-        <v>4.527598011769726</v>
+        <v>4.527598011769728</v>
       </c>
       <c r="H1966" t="n">
         <v>4.551966019141562</v>
@@ -51581,7 +51581,7 @@
         <v>4.581535043571318</v>
       </c>
       <c r="G1967" t="n">
-        <v>4.531704171463762</v>
+        <v>4.531704171463764</v>
       </c>
       <c r="H1967" t="n">
         <v>4.556619607517529</v>
@@ -51607,7 +51607,7 @@
         <v>4.588250191052846</v>
       </c>
       <c r="G1968" t="n">
-        <v>4.53966813215442</v>
+        <v>4.539668132154421</v>
       </c>
       <c r="H1968" t="n">
         <v>4.563959161603622</v>
@@ -51633,7 +51633,7 @@
         <v>4.593863795428368</v>
       </c>
       <c r="G1969" t="n">
-        <v>4.548404691951097</v>
+        <v>4.548404691951099</v>
       </c>
       <c r="H1969" t="n">
         <v>4.571134243689722</v>
@@ -51659,7 +51659,7 @@
         <v>4.5963508484121</v>
       </c>
       <c r="G1970" t="n">
-        <v>4.553990402480673</v>
+        <v>4.553990402480675</v>
       </c>
       <c r="H1970" t="n">
         <v>4.575170625446376</v>
@@ -51685,7 +51685,7 @@
         <v>4.602314787050916</v>
       </c>
       <c r="G1971" t="n">
-        <v>4.561130550266063</v>
+        <v>4.561130550266065</v>
       </c>
       <c r="H1971" t="n">
         <v>4.581722668658479</v>
@@ -51711,7 +51711,7 @@
         <v>4.577248737296835</v>
       </c>
       <c r="G1972" t="n">
-        <v>4.535050398780966</v>
+        <v>4.535050398780967</v>
       </c>
       <c r="H1972" t="n">
         <v>4.556149568038889</v>
@@ -51737,7 +51737,7 @@
         <v>4.580988175397364</v>
       </c>
       <c r="G1973" t="n">
-        <v>4.540603488684624</v>
+        <v>4.540603488684626</v>
       </c>
       <c r="H1973" t="n">
         <v>4.560795832040982</v>
@@ -51763,7 +51763,7 @@
         <v>4.582518481472182</v>
       </c>
       <c r="G1974" t="n">
-        <v>4.543314592565778</v>
+        <v>4.54331459256578</v>
       </c>
       <c r="H1974" t="n">
         <v>4.562916537018968</v>
@@ -51789,7 +51789,7 @@
         <v>4.584246382352242</v>
       </c>
       <c r="G1975" t="n">
-        <v>4.545916645415463</v>
+        <v>4.545916645415465</v>
       </c>
       <c r="H1975" t="n">
         <v>4.565081513883841</v>
@@ -51815,7 +51815,7 @@
         <v>4.601182772395505</v>
       </c>
       <c r="G1976" t="n">
-        <v>4.561914220549073</v>
+        <v>4.561914220549075</v>
       </c>
       <c r="H1976" t="n">
         <v>4.581548496472278</v>
@@ -51841,7 +51841,7 @@
         <v>4.594488733370135</v>
       </c>
       <c r="G1977" t="n">
-        <v>4.556342791988067</v>
+        <v>4.556342791988069</v>
       </c>
       <c r="H1977" t="n">
         <v>4.575415762679089</v>
@@ -51867,7 +51867,7 @@
         <v>4.608459013973127</v>
       </c>
       <c r="G1978" t="n">
-        <v>4.572208187508054</v>
+        <v>4.572208187508056</v>
       </c>
       <c r="H1978" t="n">
         <v>4.590333600740578</v>
@@ -51893,7 +51893,7 @@
         <v>4.595250654834912</v>
       </c>
       <c r="G1979" t="n">
-        <v>4.561009009643139</v>
+        <v>4.561009009643141</v>
       </c>
       <c r="H1979" t="n">
         <v>4.578129832239013</v>
@@ -51919,7 +51919,7 @@
         <v>4.58830946493879</v>
       </c>
       <c r="G1980" t="n">
-        <v>4.553905761720731</v>
+        <v>4.553905761720733</v>
       </c>
       <c r="H1980" t="n">
         <v>4.571107613329748</v>
@@ -51945,7 +51945,7 @@
         <v>4.615072283660773</v>
       </c>
       <c r="G1981" t="n">
-        <v>4.582482313240749</v>
+        <v>4.58248231324075</v>
       </c>
       <c r="H1981" t="n">
         <v>4.598777298450749</v>
@@ -51971,7 +51971,7 @@
         <v>4.599093135335208</v>
       </c>
       <c r="G1982" t="n">
-        <v>4.568621624070397</v>
+        <v>4.568621624070399</v>
       </c>
       <c r="H1982" t="n">
         <v>4.583857379702791</v>
@@ -51997,7 +51997,7 @@
         <v>4.599481374317596</v>
       </c>
       <c r="G1983" t="n">
-        <v>4.569864639344583</v>
+        <v>4.569864639344585</v>
       </c>
       <c r="H1983" t="n">
         <v>4.584673006831078</v>
@@ -52023,7 +52023,7 @@
         <v>4.56928833411023</v>
       </c>
       <c r="G1984" t="n">
-        <v>4.536239043079424</v>
+        <v>4.536239043079425</v>
       </c>
       <c r="H1984" t="n">
         <v>4.552763688594816</v>
@@ -52049,7 +52049,7 @@
         <v>4.592506859069092</v>
       </c>
       <c r="G1985" t="n">
-        <v>4.558128737629076</v>
+        <v>4.558128737629078</v>
       </c>
       <c r="H1985" t="n">
         <v>4.575317798349072</v>
@@ -52075,7 +52075,7 @@
         <v>4.59315517520651</v>
       </c>
       <c r="G1986" t="n">
-        <v>4.556717223992755</v>
+        <v>4.556717223992757</v>
       </c>
       <c r="H1986" t="n">
         <v>4.574936199599621</v>
@@ -52101,7 +52101,7 @@
         <v>4.593080463930878</v>
       </c>
       <c r="G1987" t="n">
-        <v>4.557661042150079</v>
+        <v>4.557661042150081</v>
       </c>
       <c r="H1987" t="n">
         <v>4.575370753040468</v>
@@ -52127,7 +52127,7 @@
         <v>4.609472173101617</v>
       </c>
       <c r="G1988" t="n">
-        <v>4.56874145839878</v>
+        <v>4.568741458398781</v>
       </c>
       <c r="H1988" t="n">
         <v>4.589106815750187</v>
@@ -52153,7 +52153,7 @@
         <v>4.608297585001695</v>
       </c>
       <c r="G1989" t="n">
-        <v>4.568243518377693</v>
+        <v>4.568243518377694</v>
       </c>
       <c r="H1989" t="n">
         <v>4.588270551689682</v>
@@ -52179,7 +52179,7 @@
         <v>4.614619439624911</v>
       </c>
       <c r="G1990" t="n">
-        <v>4.576292318446876</v>
+        <v>4.576292318446878</v>
       </c>
       <c r="H1990" t="n">
         <v>4.595455879035882</v>
@@ -52205,7 +52205,7 @@
         <v>4.617177339036528</v>
       </c>
       <c r="G1991" t="n">
-        <v>4.577450810259803</v>
+        <v>4.577450810259805</v>
       </c>
       <c r="H1991" t="n">
         <v>4.597314074648154</v>
@@ -52231,7 +52231,7 @@
         <v>4.604986001734229</v>
       </c>
       <c r="G1992" t="n">
-        <v>4.565291178710029</v>
+        <v>4.565291178710031</v>
       </c>
       <c r="H1992" t="n">
         <v>4.585138590222118</v>
@@ -52257,7 +52257,7 @@
         <v>4.580151596782638</v>
       </c>
       <c r="G1993" t="n">
-        <v>4.537508487226744</v>
+        <v>4.537508487226746</v>
       </c>
       <c r="H1993" t="n">
         <v>4.55883004200468</v>
@@ -52283,7 +52283,7 @@
         <v>4.593913141027424</v>
       </c>
       <c r="G1994" t="n">
-        <v>4.547879358834767</v>
+        <v>4.547879358834769</v>
       </c>
       <c r="H1994" t="n">
         <v>4.570896249931085</v>
@@ -52309,7 +52309,7 @@
         <v>4.605018483214821</v>
       </c>
       <c r="G1995" t="n">
-        <v>4.558190163120295</v>
+        <v>4.558190163120297</v>
       </c>
       <c r="H1995" t="n">
         <v>4.581604323167547</v>
@@ -52335,7 +52335,7 @@
         <v>4.598179722999698</v>
       </c>
       <c r="G1996" t="n">
-        <v>4.551849447538687</v>
+        <v>4.551849447538689</v>
       </c>
       <c r="H1996" t="n">
         <v>4.575014585269182</v>
@@ -52361,7 +52361,7 @@
         <v>4.601248733473214</v>
       </c>
       <c r="G1997" t="n">
-        <v>4.554389395249473</v>
+        <v>4.554389395249475</v>
       </c>
       <c r="H1997" t="n">
         <v>4.577819064361332</v>
@@ -52387,7 +52387,7 @@
         <v>4.605551504285853</v>
       </c>
       <c r="G1998" t="n">
-        <v>4.558590179261846</v>
+        <v>4.558590179261848</v>
       </c>
       <c r="H1998" t="n">
         <v>4.582070841773839</v>
@@ -52413,7 +52413,7 @@
         <v>4.627985084765902</v>
       </c>
       <c r="G1999" t="n">
-        <v>4.579356704042568</v>
+        <v>4.57935670404257</v>
       </c>
       <c r="H1999" t="n">
         <v>4.603670894404224</v>
@@ -52439,7 +52439,7 @@
         <v>4.684232370012928</v>
       </c>
       <c r="G2000" t="n">
-        <v>4.634710047253201</v>
+        <v>4.634710047253202</v>
       </c>
       <c r="H2000" t="n">
         <v>4.659471208633053</v>
@@ -52465,7 +52465,7 @@
         <v>4.680569111343932</v>
       </c>
       <c r="G2001" t="n">
-        <v>4.628905561069687</v>
+        <v>4.628905561069689</v>
       </c>
       <c r="H2001" t="n">
         <v>4.654737336206798</v>
@@ -52491,7 +52491,7 @@
         <v>4.772765175140007</v>
       </c>
       <c r="G2002" t="n">
-        <v>4.718593872512917</v>
+        <v>4.718593872512919</v>
       </c>
       <c r="H2002" t="n">
         <v>4.745679523826451</v>
@@ -52517,7 +52517,7 @@
         <v>4.806761038450675</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.747827126962582</v>
+        <v>4.747827126962584</v>
       </c>
       <c r="H2003" t="n">
         <v>4.777294082706617</v>
@@ -52543,7 +52543,7 @@
         <v>4.781082334057669</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.720454555772033</v>
+        <v>4.720454555772035</v>
       </c>
       <c r="H2004" t="n">
         <v>4.75076844491484</v>
@@ -52569,7 +52569,7 @@
         <v>4.804733656546771</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.742217271306396</v>
+        <v>4.742217271306398</v>
       </c>
       <c r="H2005" t="n">
         <v>4.773475463926573</v>
@@ -52595,7 +52595,7 @@
         <v>4.819711090284737</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.757117806365176</v>
+        <v>4.757117806365178</v>
       </c>
       <c r="H2006" t="n">
         <v>4.788414448324946</v>
@@ -52621,7 +52621,7 @@
         <v>4.817136795122903</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.751945351998806</v>
+        <v>4.751945351998808</v>
       </c>
       <c r="H2007" t="n">
         <v>4.784541073560844</v>
@@ -52647,7 +52647,7 @@
         <v>4.823854455912936</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.761809531321024</v>
+        <v>4.761809531321026</v>
       </c>
       <c r="H2008" t="n">
         <v>4.79283199361697</v>
@@ -52673,7 +52673,7 @@
         <v>4.854180357940738</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.796527332359263</v>
+        <v>4.796527332359265</v>
       </c>
       <c r="H2009" t="n">
         <v>4.82535384514999</v>
@@ -52699,7 +52699,7 @@
         <v>4.83830919335292</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.780722013263747</v>
+        <v>4.780722013263749</v>
       </c>
       <c r="H2010" t="n">
         <v>4.809515603308323</v>
@@ -52725,7 +52725,7 @@
         <v>4.839903292352668</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.783490827507712</v>
+        <v>4.783490827507713</v>
       </c>
       <c r="H2011" t="n">
         <v>4.811697059930179</v>
@@ -52751,7 +52751,7 @@
         <v>4.82622962117408</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.769206643263909</v>
+        <v>4.769206643263911</v>
       </c>
       <c r="H2012" t="n">
         <v>4.797718132218984</v>
@@ -52777,7 +52777,7 @@
         <v>4.805563715501266</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.749727977362742</v>
+        <v>4.749727977362744</v>
       </c>
       <c r="H2013" t="n">
         <v>4.777645846431993</v>
@@ -52803,7 +52803,7 @@
         <v>4.801056519994203</v>
       </c>
       <c r="G2014" t="n">
-        <v>4.745696421991516</v>
+        <v>4.745696421991518</v>
       </c>
       <c r="H2014" t="n">
         <v>4.773376470992849</v>
@@ -52829,7 +52829,7 @@
         <v>4.786483929175768</v>
       </c>
       <c r="G2015" t="n">
-        <v>4.733120598841063</v>
+        <v>4.733120598841065</v>
       </c>
       <c r="H2015" t="n">
         <v>4.759802264008405</v>
@@ -52855,7 +52855,7 @@
         <v>4.804861401610505</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.751548387896255</v>
+        <v>4.751548387896257</v>
       </c>
       <c r="H2016" t="n">
         <v>4.778204894753369</v>
@@ -52881,7 +52881,7 @@
         <v>4.791450357996867</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.738686938010338</v>
+        <v>4.73868693801034</v>
       </c>
       <c r="H2017" t="n">
         <v>4.765068648003592</v>
@@ -52907,7 +52907,7 @@
         <v>4.781799418899318</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.725918344351048</v>
+        <v>4.72591834435105</v>
       </c>
       <c r="H2018" t="n">
         <v>4.753858881625172</v>
@@ -52933,7 +52933,7 @@
         <v>4.784202013706425</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.73075789219357</v>
+        <v>4.730757892193572</v>
       </c>
       <c r="H2019" t="n">
         <v>4.757479952949986</v>
@@ -52959,7 +52959,7 @@
         <v>4.79257774029054</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.74102607507397</v>
+        <v>4.741026075073972</v>
       </c>
       <c r="H2020" t="n">
         <v>4.766801907682243</v>
@@ -52985,7 +52985,7 @@
         <v>4.788628952790689</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.741337177867084</v>
+        <v>4.741337177867086</v>
       </c>
       <c r="H2021" t="n">
         <v>4.764983065328875</v>
@@ -53011,7 +53011,7 @@
         <v>4.770355545344967</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.729548108037998</v>
+        <v>4.729548108037999</v>
       </c>
       <c r="H2022" t="n">
         <v>4.74995182669147</v>
